--- a/results/job_matches_2026-05-04.xlsx
+++ b/results/job_matches_2026-05-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Growth Protocol</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>Databricks, Google Cloud Platform, Spark, Scala, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aedebd419ff75231</t>
+          <t>https://www.indeed.com/viewjob?jk=73f78f46255a670f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Safety Analytics, Tools &amp; Databases</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Snowflake, Oracle, SQL Server, NoSQL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1310a0840225d1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=aedebd419ff75231</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Center/Server Administrator</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alternative Information Systems</t>
+          <t>Balfour Beatty</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,112 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc658fe2914f7423</t>
+          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Sr. Engineer - Safety Analytics, Tools &amp; Databases</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Snowflake, Oracle, SQL Server, NoSQL, Power BI</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1310a0840225d1d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>PHP Developer</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Scroll Tab</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Dallas, TX, US USA</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D9" t="n">
         <v>11.1</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c010e703dc6247a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Data Center/Server Administrator</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Alternative Information Systems</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc658fe2914f7423</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-04.xlsx
+++ b/results/job_matches_2026-05-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,60 +643,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Balfour Beatty</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9af83131be97f8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Safety Analytics, Tools &amp; Databases</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Balfour Beatty</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Snowflake, Oracle, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1310a0840225d1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PHP Developer</t>
+          <t>Sr. Engineer - Safety Analytics, Tools &amp; Databases</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Scroll Tab</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Snowflake, Oracle, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c010e703dc6247a2</t>
+          <t>https://www.indeed.com/viewjob?jk=1310a0840225d1d5</t>
         </is>
       </c>
     </row>
@@ -777,6 +777,111 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fc658fe2914f7423</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>WesBanco Bank, Inc.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bowie, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PHP Developer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Scroll Tab</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c010e703dc6247a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Power BI Specialist</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dynamic Consulting Group</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Star Schema, Dimension Tables</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e353c5cce39b1c4f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-04.xlsx
+++ b/results/job_matches_2026-05-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer (DataOps &amp; Infrastructure Focus)</t>
+          <t>Solutions Architect - Cloud Data Warehousing (GCP)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Mattel, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, Scala</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6125421c57f16e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22eed84f3a0e5a</t>
         </is>
       </c>
     </row>
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22eed84f3a0e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=54329e26a8f1201c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Solutions Architect - Cloud Data Warehousing (GCP)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mattel, Inc.</t>
+          <t>Growth Protocol</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
+          <t>Databricks, Google Cloud Platform, Spark, Scala, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54329e26a8f1201c</t>
+          <t>https://www.indeed.com/viewjob?jk=73f78f46255a670f</t>
         </is>
       </c>
     </row>
@@ -578,12 +578,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Growth Protocol</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, Spark, Scala, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f78f46255a670f</t>
+          <t>https://www.indeed.com/viewjob?jk=aedebd419ff75231</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Balfour Beatty</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aedebd419ff75231</t>
+          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Sr. Engineer - Safety Analytics, Tools &amp; Databases</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Snowflake, Oracle, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9af83131be97f8</t>
+          <t>https://www.indeed.com/viewjob?jk=1310a0840225d1d5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Balfour Beatty</t>
+          <t>Rebel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
+          <t>AWS, Glue, S3, ECS, IAM, RDS, Azure, Polars, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
+          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Safety Analytics, Tools &amp; Databases</t>
+          <t>PHP Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Scroll Tab</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Snowflake, Oracle, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1310a0840225d1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c010e703dc6247a2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Center/Server Administrator</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alternative Information Systems</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,120 +766,50 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc658fe2914f7423</t>
+          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Power BI Specialist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Dynamic Consulting Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PHP Developer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Scroll Tab</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c010e703dc6247a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Power BI Specialist</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Dynamic Consulting Group</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Star Schema, Dimension Tables</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e353c5cce39b1c4f</t>
         </is>

--- a/results/job_matches_2026-05-04.xlsx
+++ b/results/job_matches_2026-05-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Solutions Architect - Cloud Data Warehousing (GCP)</t>
+          <t>Junior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mattel, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>24.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Redshift, Azure, Databricks, Google Cloud Platform, BigQuery, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22eed84f3a0e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1612776e805e54c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Solutions Architect - Cloud Data Warehousing (GCP)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mattel, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54329e26a8f1201c</t>
+          <t>https://www.indeed.com/viewjob?jk=931e03bde1c477ea</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect - Cloud Data Warehousing (GCP)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Growth Protocol</t>
+          <t>Mattel, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, Spark, Scala, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f78f46255a670f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22eed84f3a0e5a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect - Cloud Data Warehousing (GCP)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Mattel, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,102 +601,102 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aedebd419ff75231</t>
+          <t>https://www.indeed.com/viewjob?jk=54329e26a8f1201c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Balfour Beatty</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
+          <t>https://www.indeed.com/viewjob?jk=21777f31aa4e15fc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Safety Analytics, Tools &amp; Databases</t>
+          <t>Infrastructure Engineer (Cloud Focus)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Snowflake, Oracle, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1310a0840225d1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=913dc1f0ef2502d9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Cloud Support Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rebel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, IAM, RDS, Azure, Polars, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,110 +706,495 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaf7c2a648f0705</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PHP Developer</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Scroll Tab</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c010e703dc6247a2</t>
+          <t>https://www.indeed.com/viewjob?jk=f94722145b4f2019</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Growth Protocol</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>Databricks, Google Cloud Platform, Spark, Scala, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
+          <t>https://www.indeed.com/viewjob?jk=73f78f46255a670f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Senior Cloud Disaster Recovery Architect</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b578c92e498309f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Cloud Disaster Recovery Architect</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a30ab82b34b6466</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DevOps Architect</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Oracle, MySQL, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e44cf21cb97515cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kubernetes Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ddf6f51fef293c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer (Cloud Focus)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c31d35f272797bf3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Balfour Beatty</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sr. Engineer - Safety Analytics, Tools &amp; Databases</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Snowflake, Oracle, SQL Server, NoSQL, Power BI</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1310a0840225d1d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rebel</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, ECS, IAM, RDS, Azure, Polars, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PHP Developer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Scroll Tab</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c010e703dc6247a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WesBanco Bank, Inc.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bowie, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Cloud Disaster Recovery Architect</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Jenkins, Git, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e64d1d6af8d67c0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Power BI Specialist</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Dynamic Consulting Group</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D22" t="n">
         <v>10.4</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>RDS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e353c5cce39b1c4f</t>
         </is>

--- a/results/job_matches_2026-05-04.xlsx
+++ b/results/job_matches_2026-05-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Architect</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ashapura Softech Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a30ab82b34b6466</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f96741c29b2cd0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Oracle, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e44cf21cb97515cf</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9af83131be97f8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Senior Cloud Disaster Recovery Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ddf6f51fef293c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5a30ab82b34b6466</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Cloud Focus)</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Oracle, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31d35f272797bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=e44cf21cb97515cf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Balfour Beatty</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,225 +976,365 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
+          <t>https://www.indeed.com/viewjob?jk=7ddf6f51fef293c8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Safety Analytics, Tools &amp; Databases</t>
+          <t>Infrastructure Engineer (Cloud Focus)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Snowflake, Oracle, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1310a0840225d1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c31d35f272797bf3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rebel</t>
+          <t>Balfour Beatty</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, IAM, RDS, Azure, Polars, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
+          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PHP Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Scroll Tab</t>
+          <t>Rebel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, S3, ECS, IAM, RDS, Azure, Polars, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c010e703dc6247a2</t>
+          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Software Engineering / Data Science Intern</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>BSI Financial Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
+          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Architect</t>
+          <t>Senior Data Center/Server Administrator</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alternative Information Systems</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Jenkins, Git, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64d1d6af8d67c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc658fe2914f7423</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>PHP Developer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Scroll Tab</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c010e703dc6247a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>WesBanco Bank, Inc.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bowie, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Cloud Disaster Recovery Architect</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Jenkins, Git, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e64d1d6af8d67c0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Equus Computer Systems</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>City of Industry, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ECS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Power BI Specialist</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Dynamic Consulting Group</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D26" t="n">
         <v>10.4</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>RDS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e353c5cce39b1c4f</t>
         </is>

--- a/results/job_matches_2026-05-04.xlsx
+++ b/results/job_matches_2026-05-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=931e03bde1c477ea</t>
+          <t>https://www.indeed.com/viewjob?jk=5e54c3f102344248</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Solutions Architect - Cloud Data Warehousing (GCP)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mattel, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e22eed84f3a0e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=931e03bde1c477ea</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Solutions Architect - Cloud Data Warehousing (GCP)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mattel, Inc.</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,24 +591,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54329e26a8f1201c</t>
+          <t>https://www.indeed.com/viewjob?jk=709c18d442014735</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21777f31aa4e15fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ad8bcaa8fa27acf0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Cloud Focus)</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913dc1f0ef2502d9</t>
+          <t>https://www.indeed.com/viewjob?jk=21777f31aa4e15fc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Support Engineer</t>
+          <t>Infrastructure Engineer (Cloud Focus)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaf7c2a648f0705</t>
+          <t>https://www.indeed.com/viewjob?jk=913dc1f0ef2502d9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,15 +723,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,49 +741,49 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f94722145b4f2019</t>
+          <t>https://www.indeed.com/viewjob?jk=30e1948be295dcc1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Growth Protocol</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, Spark, Scala, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f78f46255a670f</t>
+          <t>https://www.indeed.com/viewjob?jk=56ccf65ff48d085d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Architect</t>
+          <t>Cloud Support Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,15 +793,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b578c92e498309f</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaf7c2a648f0705</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ashapura Softech Pvt. Ltd.</t>
+          <t>Blue Photon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Shelby, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f96741c29b2cd0</t>
+          <t>https://www.indeed.com/viewjob?jk=ff88f005d63b8626</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9af83131be97f8</t>
+          <t>https://www.indeed.com/viewjob?jk=32d18419724cd3ba</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Architect</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,15 +898,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,49 +916,49 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a30ab82b34b6466</t>
+          <t>https://www.indeed.com/viewjob?jk=f94722145b4f2019</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Growth Protocol</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Oracle, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>Databricks, Google Cloud Platform, Spark, Scala, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e44cf21cb97515cf</t>
+          <t>https://www.indeed.com/viewjob?jk=73f78f46255a670f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,15 +968,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ddf6f51fef293c8</t>
+          <t>https://www.indeed.com/viewjob?jk=feb3059078a0901f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Cloud Focus)</t>
+          <t>Software Engineering Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Kafka, Oracle, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31d35f272797bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=d922efe548db8f2d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Balfour Beatty</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rebel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, IAM, RDS, Azure, Polars, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9ff20d039737ab</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineering / Data Science Intern</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BSI Financial Services</t>
+          <t>Lithic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,119 +1126,119 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Center/Server Administrator</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alternative Information Systems</t>
+          <t>Lithic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc658fe2914f7423</t>
+          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PHP Developer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Scroll Tab</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c010e703dc6247a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9c3f737864e384</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
+          <t>https://www.indeed.com/viewjob?jk=f095b443e497d6af</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Cloud Disaster Recovery Architect</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,15 +1248,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Jenkins, Git, Azure Monitor</t>
+          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,77 +1266,497 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64d1d6af8d67c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Equus Computer Systems</t>
+          <t>Balfour Beatty</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
+          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Power BI Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dynamic Consulting Group</t>
+          <t>Economic Mobility Systems</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=153cac663bc30f74</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Engineering / Data Science Intern</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BSI Financial Services</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Rebel</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, ECS, IAM, RDS, Azure, Polars, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AWS API Gateway Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Arvest Bank</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Database Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chess.com</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5a14d40ff745332</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Python Web Developer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Qode</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Spark, PySpark, Scala, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec34b48fe754f748</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PHP Developer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Scroll Tab</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c010e703dc6247a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>WesBanco Bank, Inc.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bowie, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Enterprise Data Modeler / Data Architect</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>STERIS</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Mentor, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>10.4</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Star Schema, Dimension Tables</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e353c5cce39b1c4f</t>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Technical Architect</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2265f7a07a9ea472</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Heygen</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Equus Computer Systems</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>City of Industry, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ECS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-04.xlsx
+++ b/results/job_matches_2026-05-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>API Designer &amp; Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Perma Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709c18d442014735</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5e3543625f308e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Software Engineer, AI &amp; Clinical Applications</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad8bcaa8fa27acf0</t>
+          <t>https://www.indeed.com/viewjob?jk=524366a1c78290a5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21777f31aa4e15fc</t>
+          <t>https://www.indeed.com/viewjob?jk=709c18d442014735</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Cloud Focus)</t>
+          <t>Senior Kafka Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global Technology Partners</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913dc1f0ef2502d9</t>
+          <t>https://www.indeed.com/viewjob?jk=99395056edb471f6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e1948be295dcc1</t>
+          <t>https://www.indeed.com/viewjob?jk=ad8bcaa8fa27acf0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ccf65ff48d085d</t>
+          <t>https://www.indeed.com/viewjob?jk=21777f31aa4e15fc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Support Engineer</t>
+          <t>Infrastructure Engineer (Cloud Focus)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaf7c2a648f0705</t>
+          <t>https://www.indeed.com/viewjob?jk=913dc1f0ef2502d9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Blue Photon</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Shelby, MI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff88f005d63b8626</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf2f712f2dc4e4d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d18419724cd3ba</t>
+          <t>https://www.indeed.com/viewjob?jk=30e1948be295dcc1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f94722145b4f2019</t>
+          <t>https://www.indeed.com/viewjob?jk=56ccf65ff48d085d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Support Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Growth Protocol</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, Spark, Scala, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f78f46255a670f</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaf7c2a648f0705</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Photon</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Shelby, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb3059078a0901f</t>
+          <t>https://www.indeed.com/viewjob?jk=ff88f005d63b8626</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor- Hybrid</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Kafka, Oracle, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,49 +1021,49 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d922efe548db8f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=f94722145b4f2019</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Growth Protocol</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
+          <t>Databricks, Google Cloud Platform, Spark, Scala, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
+          <t>https://www.indeed.com/viewjob?jk=73f78f46255a670f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1077,11 +1077,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,19 +1091,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9ff20d039737ab</t>
+          <t>https://www.indeed.com/viewjob?jk=feb3059078a0901f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lithic</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
+          <t>https://www.indeed.com/viewjob?jk=95c25d7265e67ebd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lithic</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
+          <t>https://www.indeed.com/viewjob?jk=2d959a6a5899f587</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Software Engineering Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Kafka, Oracle, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9c3f737864e384</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a12d6a95d478ec</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Software Engineering Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Kafka, Oracle, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f095b443e497d6af</t>
+          <t>https://www.indeed.com/viewjob?jk=d922efe548db8f2d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Balfour Beatty</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,42 +1291,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9ff20d039737ab</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Economic Mobility Systems</t>
+          <t>Lithic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153cac663bc30f74</t>
+          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineering / Data Science Intern</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BSI Financial Services</t>
+          <t>Lithic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rebel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, IAM, RDS, Azure, Polars, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9c3f737864e384</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
+          <t>https://www.indeed.com/viewjob?jk=f095b443e497d6af</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
+          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
+          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>Balfour Beatty</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5a14d40ff745332</t>
+          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Python Web Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Economic Mobility Systems</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, PySpark, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,102 +1546,102 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec34b48fe754f748</t>
+          <t>https://www.indeed.com/viewjob?jk=153cac663bc30f74</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PHP Developer</t>
+          <t>Software Engineering / Data Science Intern</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Scroll Tab</t>
+          <t>BSI Financial Services</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c010e703dc6247a2</t>
+          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Rebel</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Glue, S3, ECS, IAM, RDS, Azure, Polars, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
+          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>STERIS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mentor, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1672,89 +1672,439 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2265f7a07a9ea472</t>
+          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Heygen</t>
+          <t>Basis</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf3483120003abe</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Python Web Developer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Qode</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Spark, PySpark, Scala, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec34b48fe754f748</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer – Enterprise Software</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer/C# - Backend Developer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HireIO, Inc.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Hooksett, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db9d74eb17603766</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PHP Developer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Scroll Tab</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c010e703dc6247a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>WesBanco Bank, Inc.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Bowie, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>The Hershey Company</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Hershey, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Database Administrator</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ImageTrend</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Eagan, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Enterprise Data Modeler / Data Architect</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>STERIS</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Mentor, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Technical Architect</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2265f7a07a9ea472</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Heygen</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Software Engineer II</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Equus Computer Systems</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>City of Industry, CA, US USA</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D48" t="n">
         <v>10.4</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>ECS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
         </is>

--- a/results/job_matches_2026-05-04.xlsx
+++ b/results/job_matches_2026-05-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Kafka Engineer</t>
+          <t>Senior Confluent Kafka Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Support Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Photon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Shelby, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaf7c2a648f0705</t>
+          <t>https://www.indeed.com/viewjob?jk=ff88f005d63b8626</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Support Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Blue Photon</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Shelby, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff88f005d63b8626</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaf7c2a648f0705</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c25d7265e67ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=2d959a6a5899f587</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineering Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Kafka, Oracle, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d959a6a5899f587</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a12d6a95d478ec</t>
         </is>
       </c>
     </row>
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a12d6a95d478ec</t>
+          <t>https://www.indeed.com/viewjob?jk=d922efe548db8f2d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor- Hybrid</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Kafka, Oracle, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d922efe548db8f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, IAM, RDS, Oracle, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9ff20d039737ab</t>
+          <t>https://www.indeed.com/viewjob?jk=cae956ca669aed0b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lithic</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9ff20d039737ab</t>
         </is>
       </c>
     </row>
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
+          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lithic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9c3f737864e384</t>
+          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f095b443e497d6af</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9c3f737864e384</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=f095b443e497d6af</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Balfour Beatty</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Economic Mobility Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,59 +1546,59 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153cac663bc30f74</t>
+          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineering / Data Science Intern</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BSI Financial Services</t>
+          <t>Balfour Beatty</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rebel</t>
+          <t>Economic Mobility Systems</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, IAM, RDS, Azure, Polars, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
+          <t>https://www.indeed.com/viewjob?jk=153cac663bc30f74</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
+          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Software Engineering / Data Science Intern</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>BSI Financial Services</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf3483120003abe</t>
+          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Python Web Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Rebel</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, PySpark, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, ECS, IAM, RDS, Azure, Polars, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec34b48fe754f748</t>
+          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Software</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, MySQL, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
+          <t>https://www.indeed.com/viewjob?jk=f16a3c93041c1854</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer/C# - Backend Developer</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HireIO, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hooksett, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db9d74eb17603766</t>
+          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PHP Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Scroll Tab</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c010e703dc6247a2</t>
+          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Basis</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,42 +1886,42 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf3483120003abe</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Python Web Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Spark, PySpark, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,129 +1931,129 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=ec34b48fe754f748</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Software Engineer/C# - Backend Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ImageTrend</t>
+          <t>HireIO, Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Hooksett, NH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
+          <t>https://www.indeed.com/viewjob?jk=db9d74eb17603766</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
+          <t>Software Engineer – Enterprise Software</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>STERIS</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mentor, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2265f7a07a9ea472</t>
+          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Heygen</t>
+          <t>Florida Panthers</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
+          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Equus Computer Systems</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,15 +2096,225 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Database Administrator</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ImageTrend</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Eagan, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Advanced Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, PostgreSQL, ELT, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14533c5ea4cb3a4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Enterprise Data Modeler / Data Architect</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>STERIS</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Mentor, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Technical Architect</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2265f7a07a9ea472</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Heygen</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Equus Computer Systems</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>City of Industry, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>ECS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
         </is>

--- a/results/job_matches_2026-05-04.xlsx
+++ b/results/job_matches_2026-05-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,20 +508,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e54c3f102344248</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc5f1f057c765d5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=931e03bde1c477ea</t>
+          <t>https://www.indeed.com/viewjob?jk=8af28ed89b784a62</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>API Designer &amp; Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Perma Technologies</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, Azure, GCP, BigQuery, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5e3543625f308e</t>
+          <t>https://www.indeed.com/viewjob?jk=da31900dca44a1d5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer, AI &amp; Clinical Applications</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524366a1c78290a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5e54c3f102344248</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709c18d442014735</t>
+          <t>https://www.indeed.com/viewjob?jk=931e03bde1c477ea</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Confluent Kafka Engineer</t>
+          <t>API Designer &amp; Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Global Technology Partners</t>
+          <t>Perma Technologies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99395056edb471f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5e3543625f308e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Software Engineer, AI &amp; Clinical Applications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad8bcaa8fa27acf0</t>
+          <t>https://www.indeed.com/viewjob?jk=524366a1c78290a5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21777f31aa4e15fc</t>
+          <t>https://www.indeed.com/viewjob?jk=709c18d442014735</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Cloud Focus)</t>
+          <t>Senior Confluent Kafka Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global Technology Partners</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913dc1f0ef2502d9</t>
+          <t>https://www.indeed.com/viewjob?jk=99395056edb471f6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf2f712f2dc4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ad8bcaa8fa27acf0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e1948be295dcc1</t>
+          <t>https://www.indeed.com/viewjob?jk=21777f31aa4e15fc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Infrastructure Engineer (Cloud Focus)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ccf65ff48d085d</t>
+          <t>https://www.indeed.com/viewjob?jk=913dc1f0ef2502d9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Blue Photon</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Shelby, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff88f005d63b8626</t>
+          <t>https://www.indeed.com/viewjob?jk=19e02a6c8daa3abf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Support Engineer</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaf7c2a648f0705</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf2f712f2dc4e4d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,49 +1021,49 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f94722145b4f2019</t>
+          <t>https://www.indeed.com/viewjob?jk=30e1948be295dcc1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Growth Protocol</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, Spark, Scala, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f78f46255a670f</t>
+          <t>https://www.indeed.com/viewjob?jk=56ccf65ff48d085d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Cloud Support Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1077,11 +1077,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb3059078a0901f</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaf7c2a648f0705</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Blue Photon</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Shelby, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d959a6a5899f587</t>
+          <t>https://www.indeed.com/viewjob?jk=ff88f005d63b8626</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor- Hybrid</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Kafka, Oracle, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a12d6a95d478ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f94722145b4f2019</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor- Hybrid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Growth Protocol</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Kafka, Oracle, Data Modeling, CI/CD, Jenkins</t>
+          <t>Databricks, Google Cloud Platform, Spark, Scala, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d922efe548db8f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=73f78f46255a670f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Spark, Scala, NoSQL, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
+          <t>https://www.indeed.com/viewjob?jk=432ff4d5fea02cb3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DTN</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, IAM, RDS, Oracle, MySQL, DynamoDB</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae956ca669aed0b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d959a6a5899f587</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Software Engineering Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Kafka, Oracle, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9ff20d039737ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a12d6a95d478ec</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lithic</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
+          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
+          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lithic</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9c3f737864e384</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DTN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, IAM, RDS, Oracle, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f095b443e497d6af</t>
+          <t>https://www.indeed.com/viewjob?jk=cae956ca669aed0b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9ff20d039737ab</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9c3f737864e384</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Balfour Beatty</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Economic Mobility Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=153cac663bc30f74</t>
+          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>Balfour Beatty</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
+          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>Lithic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
+          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineering / Data Science Intern</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BSI Financial Services</t>
+          <t>Lithic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Rebel</t>
+          <t>Economic Mobility Systems</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, IAM, RDS, Azure, Polars, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
+          <t>https://www.indeed.com/viewjob?jk=153cac663bc30f74</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, MySQL, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16a3c93041c1854</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
+          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineering / Data Science Intern</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>BSI Financial Services</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,59 +1861,59 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
+          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>Rebel</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, S3, ECS, IAM, RDS, Azure, Polars, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf3483120003abe</t>
+          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Python Web Developer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, PySpark, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, MySQL, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec34b48fe754f748</t>
+          <t>https://www.indeed.com/viewjob?jk=f16a3c93041c1854</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer/C# - Backend Developer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HireIO, Inc.</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hooksett, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db9d74eb17603766</t>
+          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Software</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
+          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,77 +2026,77 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
+          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Florida Panthers</t>
+          <t>Basis</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf3483120003abe</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer/C# - Backend Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>HireIO, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Hooksett, NH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,94 +2106,94 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=db9d74eb17603766</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Software Engineer – Enterprise Software</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ImageTrend</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7a434536a69116</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Advanced Automation Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, ELT, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14533c5ea4cb3a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=3689d938fd4bd78c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>STERIS</t>
+          <t>Florida Panthers</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mentor, OH, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2265f7a07a9ea472</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Software Engineer (Contact Center)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Heygen</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
+          <t>https://www.indeed.com/viewjob?jk=84a3d2da599bb8c0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Equus Computer Systems</t>
+          <t>ImageTrend</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,15 +2306,190 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Advanced Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, PostgreSQL, ELT, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14533c5ea4cb3a4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Enterprise Data Modeler / Data Architect</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>STERIS</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Mentor, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MS Fabric</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a090799efcb0db1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Heygen</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=423ca554834f103a</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Equus Computer Systems</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>City of Industry, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>ECS, RDS, Azure, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
         </is>

--- a/results/job_matches_2026-05-04.xlsx
+++ b/results/job_matches_2026-05-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>API Designer &amp; Architect</t>
+          <t>Software Engineer, AI &amp; Clinical Applications</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Perma Technologies</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5e3543625f308e</t>
+          <t>https://www.indeed.com/viewjob?jk=524366a1c78290a5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer, AI &amp; Clinical Applications</t>
+          <t>GCP Data Engineer with ML</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524366a1c78290a5</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c5bf0db807c434</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Textron Aviation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709c18d442014735</t>
+          <t>https://www.indeed.com/viewjob?jk=860fef61fd793a2e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Confluent Kafka Engineer</t>
+          <t>Data Engineer, Finance Data &amp; BI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Global Technology Partners</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99395056edb471f6</t>
+          <t>https://www.indeed.com/viewjob?jk=22ee3be4c4c5272b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad8bcaa8fa27acf0</t>
+          <t>https://www.indeed.com/viewjob?jk=709c18d442014735</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer</t>
+          <t>Senior Confluent Kafka Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global Technology Partners</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21777f31aa4e15fc</t>
+          <t>https://www.indeed.com/viewjob?jk=99395056edb471f6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Cloud Focus)</t>
+          <t>Cloud Site Reliability Engineer (SRE) - Data Management &amp; Analytics Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913dc1f0ef2502d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0536c058377532e1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e02a6c8daa3abf</t>
+          <t>https://www.indeed.com/viewjob?jk=ad8bcaa8fa27acf0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Senior Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf2f712f2dc4e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=21777f31aa4e15fc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Infrastructure Engineer (Cloud Focus)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30e1948be295dcc1</t>
+          <t>https://www.indeed.com/viewjob?jk=913dc1f0ef2502d9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ccf65ff48d085d</t>
+          <t>https://www.indeed.com/viewjob?jk=19e02a6c8daa3abf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Support Engineer</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaaf7c2a648f0705</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf2f712f2dc4e4d</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f94722145b4f2019</t>
+          <t>https://www.indeed.com/viewjob?jk=30e1948be295dcc1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Growth Protocol</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, Spark, Scala, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f78f46255a670f</t>
+          <t>https://www.indeed.com/viewjob?jk=56ccf65ff48d085d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Cloud Support Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Spark, Scala, NoSQL, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432ff4d5fea02cb3</t>
+          <t>https://www.indeed.com/viewjob?jk=eaaf7c2a648f0705</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
+          <t>https://www.indeed.com/viewjob?jk=f94722145b4f2019</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Growth Protocol</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>Databricks, Google Cloud Platform, Spark, Scala, Snowflake, PostgreSQL, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d959a6a5899f587</t>
+          <t>https://www.indeed.com/viewjob?jk=73f78f46255a670f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor- Hybrid</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Kafka, Oracle, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a12d6a95d478ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e3885fad6f5950df</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Devops Engineer SR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Spark, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f0a15992ad4ab2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, HBase, Spark, Scala, MySQL, MongoDB, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b7f74e7816022c93</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
+          <t>https://www.indeed.com/viewjob?jk=4816c8c575f3d666</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DTN</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, IAM, RDS, Oracle, MySQL, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Azure, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae956ca669aed0b</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4f492a729e54b0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, API Gateway, Scala, Kafka, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9ff20d039737ab</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c8dbe9666075a2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9c3f737864e384</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Development Engineer II – Data Management, ArcGIS Enterprise</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9ee1979cb76698</t>
+          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Balfour Beatty</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc15090d375b6ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Balfour Beatty</t>
+          <t>Lithic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a704639955f34e73</t>
+          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
         </is>
       </c>
     </row>
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b514cb1820e9388e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>DevOps Engineer NEX</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lithic</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Spark, Kafka, Snowflake, dbt</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, DataOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c521f0d67306e74</t>
+          <t>https://www.indeed.com/viewjob?jk=f38954c975e9b162</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Software Engineering / Data Science Intern</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>BSI Financial Services</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
+          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>Rebel</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Glue, S3, ECS, IAM, RDS, Azure, Polars, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
+          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineering / Data Science Intern</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BSI Financial Services</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ae275d5381f8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0d1e498dcb1a27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Rebel</t>
+          <t>GPS Services, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, IAM, RDS, Azure, Polars, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00588f8665b4c11d</t>
+          <t>https://www.indeed.com/viewjob?jk=d55e498e6d48b52f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, MySQL, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16a3c93041c1854</t>
+          <t>https://www.indeed.com/viewjob?jk=d50c9d5baf2c805e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, MySQL, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
+          <t>https://www.indeed.com/viewjob?jk=f16a3c93041c1854</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AWS API Gateway Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Scala, ETL, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
+          <t>https://www.indeed.com/viewjob?jk=9b18a8ea57306c18</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS API Gateway Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
+          <t>https://www.indeed.com/viewjob?jk=583898b799180afb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf3483120003abe</t>
+          <t>https://www.indeed.com/viewjob?jk=f0f7634d581119dc</t>
         </is>
       </c>
     </row>
@@ -2183,25 +2183,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer Senior Consultant - Remote</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Florida Panthers</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, SQL Server, ELT, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=5ff3817985f88717</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineering &amp; Operations Specialist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=1fa30df0039fb6ec</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Contact Center)</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Alvys</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Medallion Architecture, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a3d2da599bb8c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8eb4e3d0876bc0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ImageTrend</t>
+          <t>Florida Panthers</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, SQS, ECS, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
+          <t>https://www.indeed.com/viewjob?jk=de7c00894f2af9e6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Advanced Automation Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, ELT, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14533c5ea4cb3a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Enterprise Data Modeler / Data Architect</t>
+          <t>Software Engineer SR - Full Stack .NET/React</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>STERIS</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mentor, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Blob Storage, GCP, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+          <t>https://www.indeed.com/viewjob?jk=899793b6f21fdc37</t>
         </is>
       </c>
     </row>
@@ -2492,6 +2492,111 @@
       <c r="G59" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=917465a6c5df167b</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Database Administrator</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ImageTrend</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Eagan, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eae40e99f47e527a</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Enterprise Data Modeler / Data Architect</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>STERIS</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Mentor, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a87bcde3a06ac6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Cloud Partner Solutions Engineer (AWS / Azure / Google Cloud)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=774e852ab9b8c1ba</t>
         </is>
       </c>
     </row>
